--- a/artfynd/A 36038-2022 artfynd.xlsx
+++ b/artfynd/A 36038-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36038-2022 artfynd.xlsx
+++ b/artfynd/A 36038-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103561795</v>
+        <v>107156132</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>1080</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rössjöholm, Sk</t>
+          <t>Nordala, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>383888.0735534664</v>
+        <v>383732</v>
       </c>
       <c r="R2" t="n">
-        <v>6243815.234399814</v>
+        <v>6243856</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,70 +756,87 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Grov bok i vägkant</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>21-692</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Salomon, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kartläggning av Ängelholms kommun 2022</t>
-        </is>
-      </c>
+          <t>Henrik Weibull, Torbjørn Høitomt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103561791</v>
+        <v>74351437</v>
       </c>
       <c r="B3" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>1118</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rössjöholm, Sk</t>
+          <t>Trolle Hallar, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>383849.7852931386</v>
+        <v>383732</v>
       </c>
       <c r="R3" t="n">
-        <v>6243776.895182938</v>
+        <v>6243858</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,25 +877,1907 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre bokskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Jätteträd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Jätteträd</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113877389</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75379</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stiftklotterlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Opegrapha vermicellifera</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kunze) J.R.Laundon</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrdala grov bok, Rössjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>383737</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6243853</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>74351428</v>
+      </c>
+      <c r="B5" t="n">
+        <v>77726</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med perithecier</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Trolle Hallar, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>383732</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6243858</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre bokskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Jätteträd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Jätteträd</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>103701905</v>
+      </c>
+      <c r="B6" t="n">
+        <v>77726</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rössjöholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>383732</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6243855</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Lars Salomon</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113877391</v>
+      </c>
+      <c r="B7" t="n">
+        <v>77726</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrdala grov bok, Rössjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>383737</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6243853</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>74351468</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97811</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trädporella</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porella platyphylla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Trolle Hallar, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>383732</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6243858</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre bokskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Jätteträd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Jätteträd</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>103701906</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97811</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trädporella</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porella platyphylla</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rössjöholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>383732</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6243855</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113877384</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97811</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Trädporella</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porella platyphylla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrdala grov bok, Rössjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>383737</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6243853</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>683030</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>N NORDALA (03C9g15), Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>383741</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6243860</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1998-03-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1998-03-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>030296151 / NECK COM / Ej bedömd (0)  / OBJ.AREA:0 ha</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jesper Lind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>74351449</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Trolle Hallar, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>383732</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6243858</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre bokskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Jättebok</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Jättebok</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>103701907</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rössjöholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>383732</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6243855</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>680056</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>N NORDALA (03C9g15), Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>383741</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6243860</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1998-03-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1998-03-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>030296151 / HOMA SER / Ej bedömd (0)  / OBJ.AREA:0 ha</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jesper Lind</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>74351458</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Trolle Hallar, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>383732</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6243858</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre bokskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Jätteträd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Jätteträd</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103701908</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rössjöholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>383732</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6243855</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113877385</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norrdala grov bok, Rössjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>383737</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6243853</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>103561791</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rössjöholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>383850</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6243777</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Lars Salomon, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>103561795</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rössjöholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>383889</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6243815</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>74351444</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Trolle Hallar, Sk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>383732</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6243858</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre bokskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Jättebok</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Jättebok</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36038-2022 artfynd.xlsx
+++ b/artfynd/A 36038-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107156132</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74351437</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113877389</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74351428</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103701905</t>
         </is>
       </c>
     </row>
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113877391</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74351468</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1575,6 +1615,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103701906</t>
         </is>
       </c>
     </row>
@@ -1679,6 +1724,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113877384</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,6 +1833,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/683030</t>
         </is>
       </c>
     </row>
@@ -1911,6 +1966,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74351449</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2012,6 +2072,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103701907</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2116,6 +2181,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/680056</t>
         </is>
       </c>
     </row>
@@ -2244,6 +2314,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74351458</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2343,6 +2418,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103701908</t>
         </is>
       </c>
     </row>
@@ -2447,6 +2527,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113877385</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2548,6 +2633,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103561791</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2649,6 +2739,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103561795</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2778,8 +2873,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74351444</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>